--- a/data/trans_orig/IP22B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22B-Habitat-trans_orig.xlsx
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21062</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33600</t>
+          <t>33166</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,22%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17277</t>
+          <t>17603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31618</t>
+          <t>31802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,66%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>527</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14479</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>23859</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>19068</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30825</t>
+          <t>29922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>36179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51872</t>
+          <t>51783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,33%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23181</t>
+          <t>23529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>22766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>33890</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54372</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20844</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27264</t>
+          <t>27810</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40780</t>
+          <t>40800</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,05%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>20373</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23350</t>
+          <t>23981</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27871</t>
+          <t>28581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41383</t>
+          <t>40819</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>10851</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>19956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>22427</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30623</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>39645</t>
+          <t>39487</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51069</t>
+          <t>51734</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>18872</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>47412</t>
+          <t>47922</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>65475</t>
+          <t>65970</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>53575</t>
+          <t>53109</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>72860</t>
+          <t>72309</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>105949</t>
+          <t>106784</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>132699</t>
+          <t>133466</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>57131</t>
+          <t>57208</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>75453</t>
+          <t>75438</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>75664</t>
+          <t>76035</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>94785</t>
+          <t>96142</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>140023</t>
+          <t>138737</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>166567</t>
+          <t>164741</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24005</t>
+          <t>23775</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37780</t>
+          <t>39103</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>54,93%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24504</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24804</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32834</t>
+          <t>31749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46614</t>
+          <t>46421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23509</t>
+          <t>22819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35442</t>
+          <t>35215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35122</t>
+          <t>34656</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48462</t>
+          <t>47596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66364</t>
+          <t>65813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23734</t>
+          <t>24057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>36206</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25004</t>
+          <t>25134</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37584</t>
+          <t>38334</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53031</t>
+          <t>53633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70999</t>
+          <t>71079</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,87%</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>440</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23070</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36278</t>
+          <t>36262</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32995</t>
+          <t>33346</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49598</t>
+          <t>48011</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>51,19%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23128</t>
+          <t>23056</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22180</t>
+          <t>22191</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35355</t>
+          <t>35208</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39780</t>
+          <t>39796</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55493</t>
+          <t>55065</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>838</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>877</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>709</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19266</t>
+          <t>19171</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>19152</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20662</t>
+          <t>20188</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35136</t>
+          <t>35985</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15964</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27432</t>
+          <t>26987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22791</t>
+          <t>22921</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33580</t>
+          <t>33974</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>41951</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>57774</t>
+          <t>58146</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>57427</t>
+          <t>57040</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>77891</t>
+          <t>77787</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>77679</t>
+          <t>78319</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>101451</t>
+          <t>102156</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>140872</t>
+          <t>140726</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>172315</t>
+          <t>172175</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>80017</t>
+          <t>80552</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>100950</t>
+          <t>101193</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>95974</t>
+          <t>96282</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>120723</t>
+          <t>120253</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>181853</t>
+          <t>183464</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>215366</t>
+          <t>216016</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21562</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>19535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15156</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>23083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28221</t>
+          <t>28190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40498</t>
+          <t>40278</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,63%</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>548</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9044</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>18090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>18980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33663</t>
+          <t>33496</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17178</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>33472</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47057</t>
+          <t>46610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,48%</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>21077</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>14597</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21064</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33493</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,59%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>18723</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14942</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>23797</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27449</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40249</t>
+          <t>40407</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>780</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>20314</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17232</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32968</t>
+          <t>32421</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43406</t>
+          <t>43298</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,72%</t>
         </is>
       </c>
     </row>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34650</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51922</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26374</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>42428</t>
+          <t>41906</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>65117</t>
+          <t>63787</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>88065</t>
+          <t>87536</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>59300</t>
+          <t>59314</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>76718</t>
+          <t>76846</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>69287</t>
+          <t>69309</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>86851</t>
+          <t>87106</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>134822</t>
+          <t>134029</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>158713</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>717</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18539</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16903</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15911</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31593</t>
+          <t>31753</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>758</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16026</t>
+          <t>16197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31885</t>
+          <t>31980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28064</t>
+          <t>29305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30720</t>
+          <t>31015</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48075</t>
+          <t>48402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,15%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10197</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15899</t>
+          <t>15983</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22167</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32002</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43822</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>793</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1723</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35987</t>
+          <t>36631</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>46378</t>
+          <t>46724</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18242</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12415</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>25984</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19453</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36717</t>
+          <t>37093</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>36578</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>57437</t>
+          <t>58511</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>62380</t>
+          <t>61777</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>78649</t>
+          <t>78912</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>65189</t>
+          <t>65552</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>84973</t>
+          <t>84357</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>131869</t>
+          <t>131681</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>156877</t>
+          <t>157602</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
